--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:28</t>
+    <t xml:space="preserve">2026-09-09 23:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:25</t>
+    <t xml:space="preserve">2026-09-17 14:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:20</t>
+    <t xml:space="preserve">2026-09-23 12:48</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -863,7 +863,9 @@
       <c r="C21" s="2" t="n">
         <v>16206</v>
       </c>
-      <c r="D21" s="2"/>
+      <c r="D21" s="2" t="n">
+        <v>2021</v>
+      </c>
       <c r="E21" s="2"/>
     </row>
     <row r="22">
@@ -876,7 +878,9 @@
       <c r="C22" s="2" t="n">
         <v>16303</v>
       </c>
-      <c r="D22" s="2"/>
+      <c r="D22" s="2" t="n">
+        <v>2021</v>
+      </c>
       <c r="E22" s="2"/>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_nuble.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t xml:space="preserve">Región</t>
   </si>
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:48</t>
+    <t xml:space="preserve">2026-10-01 23:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -126,7 +126,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Ingreso sobre la mediana nacional (%)</t>
+    <t xml:space="preserve">% bajo 50% de la mediana</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>
@@ -139,9 +139,6 @@
   </si>
   <si>
     <t xml:space="preserve">Unidad de medida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">% sobre mediana</t>
   </si>
 </sst>
 </file>
@@ -960,7 +957,7 @@
         <v>40</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:07</t>
+    <t xml:space="preserve">2026-10-02 11:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 11:20</t>
+    <t xml:space="preserve">2026-10-02 15:13</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_nuble.xlsx
@@ -93,7 +93,7 @@
     <t xml:space="preserve">Yungay</t>
   </si>
   <si>
-    <t xml:space="preserve">Ranquil</t>
+    <t xml:space="preserve">Ránquil</t>
   </si>
   <si>
     <t xml:space="preserve">Ñiquén</t>
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:13</t>
+    <t xml:space="preserve">2026-10-04 09:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringr_median_a_2021_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 09:23</t>
+    <t xml:space="preserve">2026-10-05 12:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
